--- a/data/PN23/rep1/counts.xlsx
+++ b/data/PN23/rep1/counts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vuhien/Desktop/20260326/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\sysb\user\vuhien\AG Galardini\Hien\Scanner\20260317\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965C1D54-5834-8746-BA75-E7194D05CD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28489D61-C7E9-453E-910F-DC2C977D78C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16800" yWindow="3580" windowWidth="21600" windowHeight="11300" xr2:uid="{90E1DCE1-7665-4D49-8580-410885E30459}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{90E1DCE1-7665-4D49-8580-410885E30459}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="29">
   <si>
     <t>vial</t>
   </si>
@@ -96,6 +99,24 @@
     <t>166h</t>
   </si>
   <si>
+    <t>190h</t>
+  </si>
+  <si>
+    <t>214h</t>
+  </si>
+  <si>
+    <t>238h</t>
+  </si>
+  <si>
+    <t>262h</t>
+  </si>
+  <si>
+    <t>285h</t>
+  </si>
+  <si>
+    <t>309h</t>
+  </si>
+  <si>
     <t>PL</t>
   </si>
   <si>
@@ -150,12 +171,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -171,7 +194,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -467,13 +490,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC8B656-94DD-4A46-A15D-F4805EB4FF3B}">
-  <dimension ref="A1:F113"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F197"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -484,16 +507,16 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -516,7 +539,7 @@
         <v>44000000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -539,7 +562,7 @@
         <v>130000000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -562,7 +585,7 @@
         <v>60000000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -572,20 +595,20 @@
       <c r="C5" t="s">
         <v>5</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <f>(7*(10^5))/0.01</f>
         <v>70000000</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <f>(6*(10^5))/0.01</f>
         <v>60000000</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <f>(10*(10^5))/0.01</f>
         <v>100000000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -595,20 +618,20 @@
       <c r="C6" t="s">
         <v>5</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <f>(4*(10^5))/0.01</f>
         <v>40000000</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <f>(3*(10^5))/0.01</f>
         <v>30000000</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <f>(13*(10^5))/0.01</f>
         <v>130000000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -631,7 +654,7 @@
         <v>120000000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -654,7 +677,7 @@
         <v>90000000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -674,7 +697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -694,7 +717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -714,7 +737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -734,7 +757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -755,7 +778,7 @@
         <v>101000000</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -776,7 +799,7 @@
         <v>126000000</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -797,7 +820,7 @@
         <v>107000000</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -820,7 +843,7 @@
         <v>8000000</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -843,7 +866,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -866,7 +889,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -876,19 +899,19 @@
       <c r="C19" t="s">
         <v>5</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <f>(23*(10^4))/0.01</f>
         <v>23000000</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <f>(26*(10^3))/0.01</f>
         <v>2600000</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -898,20 +921,20 @@
       <c r="C20" t="s">
         <v>5</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <f>(38*(10^4))/0.01</f>
         <v>38000000</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <f>(35*(10^4))/0.01</f>
         <v>35000000</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <f>(25*(10^4))/0.01</f>
         <v>25000000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -934,7 +957,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -957,7 +980,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -978,7 +1001,7 @@
         <v>8100000</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -998,7 +1021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -1018,7 +1041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -1038,7 +1061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1059,7 +1082,7 @@
         <v>13500000</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -1080,7 +1103,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1101,7 +1124,7 @@
         <v>61000000</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -1111,20 +1134,20 @@
       <c r="C30" t="s">
         <v>5</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="2">
         <f>(74*(10^3))/0.01</f>
         <v>7400000</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="2">
         <f>(90*(10^3))/0.01</f>
         <v>9000000</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="2">
         <f>(57*(10^3))/0.01</f>
         <v>5700000</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1134,20 +1157,20 @@
       <c r="C31" t="s">
         <v>5</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="2">
         <f>(7*(10^5))/0.01</f>
         <v>70000000</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="2">
         <f>(6*(10^5))/0.01</f>
         <v>60000000</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="2">
         <f>(24*(10^4))/0.01</f>
         <v>24000000</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -1157,20 +1180,20 @@
       <c r="C32" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="2">
         <f>(4*(10^5))/0.01</f>
         <v>40000000</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="2">
         <f>(5*(10^5))/0.01</f>
         <v>50000000</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="2">
         <f>(1*(10^5))/0.01</f>
         <v>10000000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -1180,20 +1203,20 @@
       <c r="C33" t="s">
         <v>5</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="3">
         <f>(14*(10^4))/0.01</f>
         <v>14000000</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="3">
         <f>(16*(10^3))/0.01</f>
         <v>1600000</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="3">
         <f>(1*(10^3))/0.01</f>
         <v>100000</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -1203,20 +1226,20 @@
       <c r="C34" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="3">
         <f>(22*(10^4))/0.01</f>
         <v>22000000</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="3">
         <f>(14*(10^4))/0.01</f>
         <v>14000000</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="3">
         <f>(9*(10^4))/0.01</f>
         <v>9000000</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -1226,20 +1249,20 @@
       <c r="C35" t="s">
         <v>5</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="2">
         <f>(41*(10^4))/0.01</f>
         <v>41000000</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="2">
         <f>(6*(10^5))/0.01</f>
         <v>60000000</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="2">
         <f>(54*(10^4))/0.01</f>
         <v>54000000</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -1249,20 +1272,20 @@
       <c r="C36" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="2">
         <f>(9*(10^3))/0.01</f>
         <v>900000</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="2">
         <f>(2*(10^3))/0.01</f>
         <v>200000</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="2">
         <f>(31*(10^4))/0.01</f>
         <v>31000000</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -1272,18 +1295,18 @@
       <c r="C37" t="s">
         <v>6</v>
       </c>
-      <c r="D37" s="1">
-        <v>0</v>
-      </c>
-      <c r="E37" s="1">
-        <v>0</v>
-      </c>
-      <c r="F37" s="1">
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
         <f>(68*(10^3))/0.01</f>
         <v>6800000</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -1293,17 +1316,17 @@
       <c r="C38" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
-        <v>0</v>
-      </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -1313,17 +1336,17 @@
       <c r="C39" t="s">
         <v>6</v>
       </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
-        <v>0</v>
-      </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -1333,17 +1356,17 @@
       <c r="C40" t="s">
         <v>6</v>
       </c>
-      <c r="D40" s="1">
-        <v>0</v>
-      </c>
-      <c r="E40" s="1">
-        <v>0</v>
-      </c>
-      <c r="F40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D40" s="2">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -1353,18 +1376,18 @@
       <c r="C41" t="s">
         <v>6</v>
       </c>
-      <c r="D41" s="1">
-        <v>0</v>
-      </c>
-      <c r="E41" s="1">
-        <v>0</v>
-      </c>
-      <c r="F41" s="1">
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2">
         <f>(84*(10^3))/0.01</f>
         <v>8400000</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -1374,18 +1397,18 @@
       <c r="C42" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="1">
-        <v>0</v>
-      </c>
-      <c r="E42" s="1">
-        <v>0</v>
-      </c>
-      <c r="F42" s="1">
+      <c r="D42" s="2">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
         <f>(52*(10^4))/0.01</f>
         <v>52000000</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -1395,18 +1418,18 @@
       <c r="C43" t="s">
         <v>6</v>
       </c>
-      <c r="D43" s="1">
-        <v>0</v>
-      </c>
-      <c r="E43" s="1">
-        <v>0</v>
-      </c>
-      <c r="F43" s="1">
+      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
         <f>(29*(10^4))/0.01</f>
         <v>29000000</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>3</v>
       </c>
@@ -1416,20 +1439,20 @@
       <c r="C44" t="s">
         <v>5</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="2">
         <f>(8*(10^4))/0.01</f>
         <v>8000000</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="2">
         <f>(5*(10^4))/0.01</f>
         <v>5000000</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="2">
         <f>(4*(10^4))/0.01</f>
         <v>4000000</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -1439,20 +1462,20 @@
       <c r="C45" t="s">
         <v>5</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" s="2">
         <f>(18*(10^5))/0.01</f>
         <v>180000000</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="2">
         <f>(24*(10^5))/0.01</f>
         <v>240000000</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="2">
         <f>(1*(10^5))/0.01</f>
         <v>10000000</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -1462,20 +1485,20 @@
       <c r="C46" t="s">
         <v>5</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="2">
         <f>(12*(10^5))/0.01</f>
         <v>120000000</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="2">
         <f>(8*(10^5))/0.01</f>
         <v>80000000</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="2">
         <f>(1*(10^5))/0.01</f>
         <v>10000000</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -1485,20 +1508,20 @@
       <c r="C47" t="s">
         <v>5</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="3">
         <f>(40*(10^3))/0.01</f>
         <v>4000000</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="3">
         <f>(9*(10^3))/0.01</f>
         <v>900000</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="3">
         <f>(1*(10^3))/0.01</f>
         <v>100000</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -1508,20 +1531,20 @@
       <c r="C48" t="s">
         <v>5</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" s="3">
         <f>(10*(10^4))/0.01</f>
         <v>10000000</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="3">
         <f>(4*(10^4))/0.01</f>
         <v>4000000</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="3">
         <f>(6*(10^4))/0.01</f>
         <v>6000000</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -1531,20 +1554,20 @@
       <c r="C49" t="s">
         <v>5</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="2">
         <f>(25*(10^5))/0.01</f>
         <v>250000000</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="2">
         <f>(48*(10^5))/0.01</f>
         <v>480000000</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="2">
         <f>(2*(10^5))/0.01</f>
         <v>20000000</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>12</v>
       </c>
@@ -1554,20 +1577,20 @@
       <c r="C50" t="s">
         <v>5</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" s="2">
         <f>(21*(10^2))/0.01</f>
         <v>210000</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="2">
         <f>(7*(10^2))/0.01</f>
         <v>70000</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="2">
         <f>(15*(10^4))/0.01</f>
         <v>15000000</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -1577,18 +1600,18 @@
       <c r="C51" t="s">
         <v>6</v>
       </c>
-      <c r="D51" s="1">
-        <v>0</v>
-      </c>
-      <c r="E51" s="1">
-        <v>0</v>
-      </c>
-      <c r="F51" s="1">
+      <c r="D51" s="2">
+        <v>0</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2">
         <f>(39*(10^3))/0.01</f>
         <v>3900000</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1598,17 +1621,17 @@
       <c r="C52" t="s">
         <v>6</v>
       </c>
-      <c r="D52" s="1">
-        <v>0</v>
-      </c>
-      <c r="E52" s="1">
-        <v>0</v>
-      </c>
-      <c r="F52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D52" s="2">
+        <v>0</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -1618,17 +1641,17 @@
       <c r="C53" t="s">
         <v>6</v>
       </c>
-      <c r="D53" s="1">
-        <v>0</v>
-      </c>
-      <c r="E53" s="1">
-        <v>0</v>
-      </c>
-      <c r="F53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D53" s="2">
+        <v>0</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -1638,17 +1661,17 @@
       <c r="C54" t="s">
         <v>6</v>
       </c>
-      <c r="D54" s="1">
-        <v>0</v>
-      </c>
-      <c r="E54" s="1">
-        <v>0</v>
-      </c>
-      <c r="F54" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D54" s="2">
+        <v>0</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>10</v>
       </c>
@@ -1658,18 +1681,18 @@
       <c r="C55" t="s">
         <v>6</v>
       </c>
-      <c r="D55" s="1">
-        <v>0</v>
-      </c>
-      <c r="E55" s="1">
-        <v>0</v>
-      </c>
-      <c r="F55" s="1">
+      <c r="D55" s="2">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2">
         <f>(54*(10^3))/0.01</f>
         <v>5400000</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -1679,18 +1702,18 @@
       <c r="C56" t="s">
         <v>6</v>
       </c>
-      <c r="D56" s="1">
-        <v>0</v>
-      </c>
-      <c r="E56" s="1">
-        <v>0</v>
-      </c>
-      <c r="F56" s="1">
+      <c r="D56" s="2">
+        <v>0</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2">
         <f>(64*(10^3))/0.01</f>
         <v>6400000</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>12</v>
       </c>
@@ -1700,18 +1723,18 @@
       <c r="C57" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="1">
-        <v>0</v>
-      </c>
-      <c r="E57" s="1">
-        <v>0</v>
-      </c>
-      <c r="F57" s="1">
+      <c r="D57" s="2">
+        <v>0</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2">
         <f>(125*(10^3))/0.01</f>
         <v>12500000</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>3</v>
       </c>
@@ -1721,20 +1744,20 @@
       <c r="C58" t="s">
         <v>5</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" s="2">
         <f>(27*(10^4))/0.01</f>
         <v>27000000</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="2">
         <f>(13*(10^4))/0.01</f>
         <v>13000000</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="2">
         <f>(2*(10^4))/0.01</f>
         <v>2000000</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -1744,19 +1767,19 @@
       <c r="C59" t="s">
         <v>5</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" s="2">
         <f>(14*(10^5))/0.01</f>
         <v>140000000</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="2">
         <f>(19*(10^5))/0.01</f>
         <v>190000000</v>
       </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -1766,20 +1789,20 @@
       <c r="C60" t="s">
         <v>5</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D60" s="2">
         <f>(26*(10^1))/0.01</f>
         <v>26000</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="2">
         <f>(56*(10^2))/0.01</f>
         <v>560000</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="2">
         <f>(46*(10^2))/0.01</f>
         <v>460000</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -1789,19 +1812,19 @@
       <c r="C61" t="s">
         <v>5</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D61" s="2">
         <f>(6*(10^4))/0.01</f>
         <v>6000000</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="2">
         <f>(3*(10^4))/0.01</f>
         <v>3000000</v>
       </c>
-      <c r="F61" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -1811,20 +1834,20 @@
       <c r="C62" t="s">
         <v>5</v>
       </c>
-      <c r="D62" s="1">
+      <c r="D62" s="2">
         <f>(31*(10^4))/0.01</f>
         <v>31000000</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62" s="2">
         <f t="shared" ref="E62" si="0">(8*(10^4))/0.01</f>
         <v>8000000</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="2">
         <f>(3*(10^4))/0.01</f>
         <v>3000000</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -1834,19 +1857,19 @@
       <c r="C63" t="s">
         <v>5</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D63" s="2">
         <f>(5*(10^5))/0.01</f>
         <v>50000000</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E63" s="2">
         <f>(6*(10^5))/0.01</f>
         <v>60000000</v>
       </c>
-      <c r="F63" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F63" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -1856,20 +1879,20 @@
       <c r="C64" t="s">
         <v>5</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D64" s="2">
         <f>(7*(10^2))/0.01</f>
         <v>70000</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64" s="2">
         <f>(9*(10^2))/0.01</f>
         <v>90000</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="2">
         <f>(11*(10^4))/0.01</f>
         <v>11000000</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>3</v>
       </c>
@@ -1879,18 +1902,18 @@
       <c r="C65" t="s">
         <v>6</v>
       </c>
-      <c r="D65" s="1">
-        <v>0</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0</v>
-      </c>
-      <c r="F65" s="1">
+      <c r="D65" s="2">
+        <v>0</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2">
         <f>(23*(10^3))/0.01</f>
         <v>2300000</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -1900,17 +1923,17 @@
       <c r="C66" t="s">
         <v>6</v>
       </c>
-      <c r="D66" s="1">
-        <v>0</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0</v>
-      </c>
-      <c r="F66" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D66" s="2">
+        <v>0</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -1920,17 +1943,17 @@
       <c r="C67" t="s">
         <v>6</v>
       </c>
-      <c r="D67" s="1">
-        <v>0</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0</v>
-      </c>
-      <c r="F67" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D67" s="2">
+        <v>0</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0</v>
+      </c>
+      <c r="F67" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -1940,17 +1963,17 @@
       <c r="C68" t="s">
         <v>6</v>
       </c>
-      <c r="D68" s="1">
-        <v>0</v>
-      </c>
-      <c r="E68" s="1">
-        <v>0</v>
-      </c>
-      <c r="F68" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D68" s="2">
+        <v>0</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>10</v>
       </c>
@@ -1960,20 +1983,20 @@
       <c r="C69" t="s">
         <v>6</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D69" s="2">
         <f>(1*(10^1))/0.01</f>
         <v>1000</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E69" s="2">
         <f>(1*(10^2))/0.01</f>
         <v>10000</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="2">
         <f>(28*(10^3))/0.01</f>
         <v>2800000</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -1983,20 +2006,20 @@
       <c r="C70" t="s">
         <v>6</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D70" s="2">
         <f>(2*(10^1))/0.01</f>
         <v>2000</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70" s="2">
         <f>(5*(10^1))/0.01</f>
         <v>5000</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="2">
         <f>(68*(10^2))/0.01</f>
         <v>680000</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>12</v>
       </c>
@@ -2006,18 +2029,18 @@
       <c r="C71" t="s">
         <v>6</v>
       </c>
-      <c r="D71" s="1">
-        <v>0</v>
-      </c>
-      <c r="E71" s="1">
-        <v>0</v>
-      </c>
-      <c r="F71" s="1">
+      <c r="D71" s="2">
+        <v>0</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2">
         <f>(61*(10^3))/0.01</f>
         <v>6100000</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>3</v>
       </c>
@@ -2027,19 +2050,19 @@
       <c r="C72" t="s">
         <v>5</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D72" s="2">
         <f>(15*(10^5))/0.01</f>
         <v>150000000</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72" s="2">
         <f>(10*(10^5))/0.01</f>
         <v>100000000</v>
       </c>
-      <c r="F72" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F72" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -2049,19 +2072,19 @@
       <c r="C73" t="s">
         <v>5</v>
       </c>
-      <c r="D73" s="1">
+      <c r="D73" s="2">
         <f>(37*(10^4))/0.01</f>
         <v>37000000</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73" s="2">
         <f>(56*(10^4))/0.01</f>
         <v>56000000</v>
       </c>
-      <c r="F73" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F73" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -2071,20 +2094,20 @@
       <c r="C74" t="s">
         <v>5</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D74" s="2">
         <f>(28*(10^3))/0.01</f>
         <v>2800000</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E74" s="2">
         <f>(14*(10^3))/0.01</f>
         <v>1400000</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="2">
         <f t="shared" ref="F74" si="1">(27*(10^4))/0.01</f>
         <v>27000000</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>9</v>
       </c>
@@ -2094,19 +2117,19 @@
       <c r="C75" t="s">
         <v>5</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D75" s="2">
         <f>(29*(10^4))/0.01</f>
         <v>29000000</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E75" s="2">
         <f>(3*(10^4))/0.01</f>
         <v>3000000</v>
       </c>
-      <c r="F75" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F75" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>10</v>
       </c>
@@ -2116,19 +2139,19 @@
       <c r="C76" t="s">
         <v>5</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D76" s="2">
         <f>(9*(10^5))/0.01</f>
         <v>90000000</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E76" s="2">
         <f>(20*(10^5))/0.01</f>
         <v>200000000</v>
       </c>
-      <c r="F76" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F76" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -2138,19 +2161,19 @@
       <c r="C77" t="s">
         <v>5</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D77" s="2">
         <f>(84*(10^4))/0.01</f>
         <v>84000000</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E77" s="2">
         <f>(11*(10^4))/0.01</f>
         <v>11000000</v>
       </c>
-      <c r="F77" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F77" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>12</v>
       </c>
@@ -2160,18 +2183,18 @@
       <c r="C78" t="s">
         <v>5</v>
       </c>
-      <c r="D78" s="1">
-        <v>0</v>
-      </c>
-      <c r="E78" s="1">
-        <v>0</v>
-      </c>
-      <c r="F78" s="1">
+      <c r="D78" s="2">
+        <v>0</v>
+      </c>
+      <c r="E78" s="2">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2">
         <f>(36*(10^3))/0.01</f>
         <v>3600000</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>3</v>
       </c>
@@ -2181,18 +2204,18 @@
       <c r="C79" t="s">
         <v>6</v>
       </c>
-      <c r="D79" s="1">
-        <v>0</v>
-      </c>
-      <c r="E79" s="1">
-        <v>0</v>
-      </c>
-      <c r="F79" s="1">
+      <c r="D79" s="2">
+        <v>0</v>
+      </c>
+      <c r="E79" s="2">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2">
         <f>(44*(10^2))/0.01</f>
         <v>440000</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>7</v>
       </c>
@@ -2202,17 +2225,17 @@
       <c r="C80" t="s">
         <v>6</v>
       </c>
-      <c r="D80" s="1">
-        <v>0</v>
-      </c>
-      <c r="E80" s="1">
-        <v>0</v>
-      </c>
-      <c r="F80" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D80" s="2">
+        <v>0</v>
+      </c>
+      <c r="E80" s="2">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -2222,17 +2245,17 @@
       <c r="C81" t="s">
         <v>6</v>
       </c>
-      <c r="D81" s="1">
-        <v>0</v>
-      </c>
-      <c r="E81" s="1">
-        <v>0</v>
-      </c>
-      <c r="F81" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D81" s="2">
+        <v>0</v>
+      </c>
+      <c r="E81" s="2">
+        <v>0</v>
+      </c>
+      <c r="F81" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>9</v>
       </c>
@@ -2242,17 +2265,17 @@
       <c r="C82" t="s">
         <v>6</v>
       </c>
-      <c r="D82" s="1">
-        <v>0</v>
-      </c>
-      <c r="E82" s="1">
-        <v>0</v>
-      </c>
-      <c r="F82" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D82" s="2">
+        <v>0</v>
+      </c>
+      <c r="E82" s="2">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>10</v>
       </c>
@@ -2262,20 +2285,20 @@
       <c r="C83" t="s">
         <v>6</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D83" s="2">
         <f>(11*(10^1))/0.01</f>
         <v>11000</v>
       </c>
-      <c r="E83" s="1">
+      <c r="E83" s="2">
         <f>(7*(10^1))/0.01</f>
         <v>7000</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="2">
         <f>(8*(10^3))/0.01</f>
         <v>800000</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -2285,20 +2308,20 @@
       <c r="C84" t="s">
         <v>6</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D84" s="2">
         <f>(30*(10^1))/0.01</f>
         <v>30000</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E84" s="2">
         <f>(11*(10^1))/0.01</f>
         <v>11000</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84" s="2">
         <f>(12*(10^2))/0.01</f>
         <v>120000</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>12</v>
       </c>
@@ -2308,18 +2331,18 @@
       <c r="C85" t="s">
         <v>6</v>
       </c>
-      <c r="D85" s="1">
-        <v>0</v>
-      </c>
-      <c r="E85" s="1">
-        <v>0</v>
-      </c>
-      <c r="F85" s="1">
+      <c r="D85" s="2">
+        <v>0</v>
+      </c>
+      <c r="E85" s="2">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2">
         <f>(34*(10^3))/0.01</f>
         <v>3400000</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>3</v>
       </c>
@@ -2329,19 +2352,19 @@
       <c r="C86" t="s">
         <v>5</v>
       </c>
-      <c r="D86" s="1">
+      <c r="D86" s="2">
         <f>(12*(10^5))/0.01</f>
         <v>120000000</v>
       </c>
-      <c r="E86" s="1">
+      <c r="E86" s="2">
         <f>(4*(10^5))/0.01</f>
         <v>40000000</v>
       </c>
-      <c r="F86" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F86" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>7</v>
       </c>
@@ -2351,20 +2374,20 @@
       <c r="C87" t="s">
         <v>5</v>
       </c>
-      <c r="D87" s="1">
+      <c r="D87" s="2">
         <f>(22*(10^4))/0.01</f>
         <v>22000000</v>
       </c>
-      <c r="E87" s="1">
+      <c r="E87" s="2">
         <f>(22*(10^4))/0.01</f>
         <v>22000000</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87" s="2">
         <f>(1*(10^4))/0.01</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -2374,20 +2397,20 @@
       <c r="C88" t="s">
         <v>5</v>
       </c>
-      <c r="D88" s="1">
+      <c r="D88" s="2">
         <f>(24*(10^4))/0.01</f>
         <v>24000000</v>
       </c>
-      <c r="E88" s="1">
+      <c r="E88" s="2">
         <f>(6*(10^4))/0.01</f>
         <v>6000000</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88" s="2">
         <f t="shared" ref="F88" si="2">(27*(10^4))/0.01</f>
         <v>27000000</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>9</v>
       </c>
@@ -2397,19 +2420,19 @@
       <c r="C89" t="s">
         <v>5</v>
       </c>
-      <c r="D89" s="1">
+      <c r="D89" s="2">
         <f>(29*(10^4))/0.01</f>
         <v>29000000</v>
       </c>
-      <c r="E89" s="1">
+      <c r="E89" s="2">
         <f>(3*(10^4))/0.01</f>
         <v>3000000</v>
       </c>
-      <c r="F89" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F89" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>10</v>
       </c>
@@ -2419,19 +2442,19 @@
       <c r="C90" t="s">
         <v>5</v>
       </c>
-      <c r="D90" s="1">
+      <c r="D90" s="2">
         <f>(16*(10^5))/0.01</f>
         <v>160000000</v>
       </c>
-      <c r="E90" s="1">
+      <c r="E90" s="2">
         <f>(37*(10^5))/0.01</f>
         <v>370000000</v>
       </c>
-      <c r="F90" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F90" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -2441,19 +2464,19 @@
       <c r="C91" t="s">
         <v>5</v>
       </c>
-      <c r="D91" s="1">
+      <c r="D91" s="2">
         <f>(18*(10^3))/0.01</f>
         <v>1800000</v>
       </c>
-      <c r="E91" s="1">
+      <c r="E91" s="2">
         <f>(4*(10^3))/0.01</f>
         <v>400000</v>
       </c>
-      <c r="F91" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F91" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>12</v>
       </c>
@@ -2463,20 +2486,20 @@
       <c r="C92" t="s">
         <v>5</v>
       </c>
-      <c r="D92" s="1">
+      <c r="D92" s="2">
         <f>(6*(10^1))/0.01</f>
         <v>6000</v>
       </c>
-      <c r="E92" s="1">
+      <c r="E92" s="2">
         <f>(1*(10^1))/0.01</f>
         <v>1000</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92" s="2">
         <f>(58*(10^2))/0.01</f>
         <v>580000</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>3</v>
       </c>
@@ -2486,18 +2509,18 @@
       <c r="C93" t="s">
         <v>6</v>
       </c>
-      <c r="D93" s="1">
-        <v>0</v>
-      </c>
-      <c r="E93" s="1">
-        <v>0</v>
-      </c>
-      <c r="F93" s="1">
+      <c r="D93" s="2">
+        <v>0</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2">
         <f>(12*(10^2))/0.01</f>
         <v>120000</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>7</v>
       </c>
@@ -2507,17 +2530,17 @@
       <c r="C94" t="s">
         <v>6</v>
       </c>
-      <c r="D94" s="1">
-        <v>0</v>
-      </c>
-      <c r="E94" s="1">
-        <v>0</v>
-      </c>
-      <c r="F94" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D94" s="2">
+        <v>0</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -2527,17 +2550,17 @@
       <c r="C95" t="s">
         <v>6</v>
       </c>
-      <c r="D95" s="1">
-        <v>0</v>
-      </c>
-      <c r="E95" s="1">
-        <v>0</v>
-      </c>
-      <c r="F95" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D95" s="2">
+        <v>0</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>9</v>
       </c>
@@ -2547,17 +2570,17 @@
       <c r="C96" t="s">
         <v>6</v>
       </c>
-      <c r="D96" s="1">
-        <v>0</v>
-      </c>
-      <c r="E96" s="1">
-        <v>0</v>
-      </c>
-      <c r="F96" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D96" s="2">
+        <v>0</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>10</v>
       </c>
@@ -2567,20 +2590,20 @@
       <c r="C97" t="s">
         <v>6</v>
       </c>
-      <c r="D97" s="1">
+      <c r="D97" s="2">
         <f>(28*(10^1))/0.01</f>
         <v>28000</v>
       </c>
-      <c r="E97" s="1">
+      <c r="E97" s="2">
         <f>(17*(10^1))/0.01</f>
         <v>17000</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97" s="2">
         <f>(34*(10^2))/0.01</f>
         <v>340000</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -2590,20 +2613,20 @@
       <c r="C98" t="s">
         <v>6</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D98" s="2">
         <f>(6*(10^1))/0.01</f>
         <v>6000</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E98" s="2">
         <f>(7*(10^2))/0.01</f>
         <v>70000</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="2">
         <f>(5*(10^1))/0.01</f>
         <v>5000</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>12</v>
       </c>
@@ -2613,18 +2636,18 @@
       <c r="C99" t="s">
         <v>6</v>
       </c>
-      <c r="D99" s="1">
-        <v>0</v>
-      </c>
-      <c r="E99" s="1">
-        <v>0</v>
-      </c>
-      <c r="F99" s="1">
+      <c r="D99" s="2">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2">
         <f>(26*(10^2))/0.01</f>
         <v>260000</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>3</v>
       </c>
@@ -2634,20 +2657,20 @@
       <c r="C100" t="s">
         <v>5</v>
       </c>
-      <c r="D100" s="1">
+      <c r="D100" s="2">
         <f>(2*(10^4))/0.01</f>
         <v>2000000</v>
       </c>
-      <c r="E100" s="1">
+      <c r="E100" s="2">
         <f>(15*(10^4))/0.01</f>
         <v>15000000</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100" s="2">
         <f>(2*(10^3))/0.01</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>7</v>
       </c>
@@ -2657,19 +2680,19 @@
       <c r="C101" t="s">
         <v>5</v>
       </c>
-      <c r="D101" s="1">
+      <c r="D101" s="2">
         <f>(20*(10^4))/0.01</f>
         <v>20000000</v>
       </c>
-      <c r="E101" s="1">
+      <c r="E101" s="2">
         <f>(16*(10^4))/0.01</f>
         <v>16000000</v>
       </c>
-      <c r="F101" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F101" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>8</v>
       </c>
@@ -2679,20 +2702,20 @@
       <c r="C102" t="s">
         <v>5</v>
       </c>
-      <c r="D102" s="1">
+      <c r="D102" s="2">
         <f>(4*(10^4))/0.01</f>
         <v>4000000</v>
       </c>
-      <c r="E102" s="1">
+      <c r="E102" s="2">
         <f>(25*(10^4))/0.01</f>
         <v>25000000</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102" s="2">
         <f>(2*(10^3))/0.01</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>9</v>
       </c>
@@ -2702,19 +2725,19 @@
       <c r="C103" t="s">
         <v>5</v>
       </c>
-      <c r="D103" s="1">
+      <c r="D103" s="2">
         <f>(61*(10^4))/0.01</f>
         <v>61000000</v>
       </c>
-      <c r="E103" s="1">
+      <c r="E103" s="2">
         <f>(87*(10^4))/0.01</f>
         <v>87000000</v>
       </c>
-      <c r="F103" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F103" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>10</v>
       </c>
@@ -2724,19 +2747,19 @@
       <c r="C104" t="s">
         <v>5</v>
       </c>
-      <c r="D104" s="1">
+      <c r="D104" s="2">
         <f>(46*(10^4))/0.01</f>
         <v>46000000</v>
       </c>
-      <c r="E104" s="1">
+      <c r="E104" s="2">
         <f>(38*(10^4))/0.01</f>
         <v>38000000</v>
       </c>
-      <c r="F104" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F104" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -2746,19 +2769,19 @@
       <c r="C105" t="s">
         <v>5</v>
       </c>
-      <c r="D105" s="1">
+      <c r="D105" s="2">
         <f>(33*(10^2))/0.01</f>
         <v>330000</v>
       </c>
-      <c r="E105" s="1">
+      <c r="E105" s="2">
         <f>(38*(10^3))/0.01</f>
         <v>3800000</v>
       </c>
-      <c r="F105" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F105" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>12</v>
       </c>
@@ -2768,18 +2791,18 @@
       <c r="C106" t="s">
         <v>5</v>
       </c>
-      <c r="D106" s="1">
-        <v>0</v>
-      </c>
-      <c r="E106" s="1">
-        <v>0</v>
-      </c>
-      <c r="F106" s="1">
+      <c r="D106" s="2">
+        <v>0</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2">
         <f>(4*(10^1))/0.01</f>
         <v>4000</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>3</v>
       </c>
@@ -2789,18 +2812,18 @@
       <c r="C107" t="s">
         <v>6</v>
       </c>
-      <c r="D107" s="1">
-        <v>0</v>
-      </c>
-      <c r="E107" s="1">
-        <v>0</v>
-      </c>
-      <c r="F107" s="1">
+      <c r="D107" s="2">
+        <v>0</v>
+      </c>
+      <c r="E107" s="2">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2">
         <f>(37*(1))/0.01</f>
         <v>3700</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>7</v>
       </c>
@@ -2810,17 +2833,17 @@
       <c r="C108" t="s">
         <v>6</v>
       </c>
-      <c r="D108" s="1">
-        <v>0</v>
-      </c>
-      <c r="E108" s="1">
-        <v>0</v>
-      </c>
-      <c r="F108" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D108" s="2">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2">
+        <v>0</v>
+      </c>
+      <c r="F108" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>8</v>
       </c>
@@ -2830,17 +2853,17 @@
       <c r="C109" t="s">
         <v>6</v>
       </c>
-      <c r="D109" s="1">
-        <v>0</v>
-      </c>
-      <c r="E109" s="1">
-        <v>0</v>
-      </c>
-      <c r="F109" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D109" s="2">
+        <v>0</v>
+      </c>
+      <c r="E109" s="2">
+        <v>0</v>
+      </c>
+      <c r="F109" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
@@ -2850,17 +2873,17 @@
       <c r="C110" t="s">
         <v>6</v>
       </c>
-      <c r="D110" s="1">
-        <v>0</v>
-      </c>
-      <c r="E110" s="1">
-        <v>0</v>
-      </c>
-      <c r="F110" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D110" s="2">
+        <v>0</v>
+      </c>
+      <c r="E110" s="2">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>10</v>
       </c>
@@ -2870,20 +2893,20 @@
       <c r="C111" t="s">
         <v>6</v>
       </c>
-      <c r="D111" s="1">
+      <c r="D111" s="2">
         <f>(16*(10^1))/0.01</f>
         <v>16000</v>
       </c>
-      <c r="E111" s="1">
+      <c r="E111" s="2">
         <f>(6*(10^1))/0.01</f>
         <v>6000</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111" s="2">
         <f>(36*(10^1))/0.01</f>
         <v>36000</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>11</v>
       </c>
@@ -2893,19 +2916,19 @@
       <c r="C112" t="s">
         <v>6</v>
       </c>
-      <c r="D112" s="1">
+      <c r="D112" s="2">
         <f>(5*(10^2))/0.01</f>
         <v>50000</v>
       </c>
-      <c r="E112" s="1">
+      <c r="E112" s="2">
         <f>(32*(10^3))/0.01</f>
         <v>3200000</v>
       </c>
-      <c r="F112" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F112" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>12</v>
       </c>
@@ -2915,15 +2938,1827 @@
       <c r="C113" t="s">
         <v>6</v>
       </c>
-      <c r="D113" s="1">
-        <v>0</v>
-      </c>
-      <c r="E113" s="1">
-        <v>0</v>
-      </c>
-      <c r="F113" s="1">
+      <c r="D113" s="2">
+        <v>0</v>
+      </c>
+      <c r="E113" s="2">
+        <v>0</v>
+      </c>
+      <c r="F113" s="2">
         <f>(2*(1))/0.01</f>
         <v>200</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" s="2">
+        <f>(26*(10^2))/0.01</f>
+        <v>260000</v>
+      </c>
+      <c r="E114" s="2">
+        <f>(28*(10^3))/0.01</f>
+        <v>2800000</v>
+      </c>
+      <c r="F114" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D115" s="2">
+        <f>(33*(10^4))/0.01</f>
+        <v>33000000</v>
+      </c>
+      <c r="E115" s="2">
+        <f>(25*(10^4))/0.01</f>
+        <v>25000000</v>
+      </c>
+      <c r="F115" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D116" s="2">
+        <v>0</v>
+      </c>
+      <c r="E116" s="2">
+        <f>(18*(10^4))/0.01</f>
+        <v>18000000</v>
+      </c>
+      <c r="F116" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D117" s="2">
+        <f>(18*(10^3))/0.01</f>
+        <v>1800000</v>
+      </c>
+      <c r="E117" s="2">
+        <f>(24*(10^3))/0.01</f>
+        <v>2400000</v>
+      </c>
+      <c r="F117" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" s="2">
+        <f>(35*(10^4))/0.01</f>
+        <v>35000000</v>
+      </c>
+      <c r="E118" s="2">
+        <f>(46*(10^4))/0.01</f>
+        <v>46000000</v>
+      </c>
+      <c r="F118" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" s="2">
+        <f>(33*(10^4))/0.01</f>
+        <v>33000000</v>
+      </c>
+      <c r="E119" s="2">
+        <f>(60*(10^3))/0.01</f>
+        <v>6000000</v>
+      </c>
+      <c r="F119" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" s="2">
+        <v>0</v>
+      </c>
+      <c r="E120" s="2">
+        <f>(1*(10^0))/0.01</f>
+        <v>100</v>
+      </c>
+      <c r="F120" s="2">
+        <f>(1*(10^0))/0.01</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D121" s="2">
+        <f>(1*(10^0))/0.01</f>
+        <v>100</v>
+      </c>
+      <c r="E121" s="2">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2">
+        <f>(67*(10^0))/0.01</f>
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D122" s="2">
+        <v>0</v>
+      </c>
+      <c r="E122" s="2">
+        <v>0</v>
+      </c>
+      <c r="F122" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D123" s="2">
+        <v>0</v>
+      </c>
+      <c r="E123" s="2">
+        <v>0</v>
+      </c>
+      <c r="F123" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D124" s="2">
+        <v>0</v>
+      </c>
+      <c r="E124" s="2">
+        <v>0</v>
+      </c>
+      <c r="F124" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D125" s="2">
+        <f>(4*(10^1))/0.01</f>
+        <v>4000</v>
+      </c>
+      <c r="E125" s="2">
+        <f>(4*(10^1))/0.01</f>
+        <v>4000</v>
+      </c>
+      <c r="F125" s="2">
+        <f>(22*(10^1))/0.01</f>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D126" s="2">
+        <f>(10*(10^1))/0.01</f>
+        <v>10000</v>
+      </c>
+      <c r="E126" s="2">
+        <f>(52*(10^2))/0.01</f>
+        <v>520000</v>
+      </c>
+      <c r="F126" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D127" s="2">
+        <v>0</v>
+      </c>
+      <c r="E127" s="2">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>3</v>
+      </c>
+      <c r="B128" t="s">
+        <v>21</v>
+      </c>
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" s="2">
+        <f>(16*(10^4))/0.01</f>
+        <v>16000000</v>
+      </c>
+      <c r="E128" s="2">
+        <f>(14*(10^2))/0.01</f>
+        <v>140000</v>
+      </c>
+      <c r="F128" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>7</v>
+      </c>
+      <c r="B129" t="s">
+        <v>21</v>
+      </c>
+      <c r="C129" t="s">
+        <v>5</v>
+      </c>
+      <c r="D129" s="2">
+        <f>(2*(10^2))/0.01</f>
+        <v>20000</v>
+      </c>
+      <c r="E129" s="2">
+        <f>(57*(10^2))/0.01</f>
+        <v>570000</v>
+      </c>
+      <c r="F129" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>8</v>
+      </c>
+      <c r="B130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C130" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" s="2">
+        <f>(23*(10^4))/0.01</f>
+        <v>23000000</v>
+      </c>
+      <c r="E130" s="2">
+        <f>(18*(10^4))/0.01</f>
+        <v>18000000</v>
+      </c>
+      <c r="F130" s="2">
+        <f>(14*(10^3))/0.01</f>
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>9</v>
+      </c>
+      <c r="B131" t="s">
+        <v>21</v>
+      </c>
+      <c r="C131" t="s">
+        <v>5</v>
+      </c>
+      <c r="D131" s="2">
+        <f>(33*(10^2))/0.01</f>
+        <v>330000</v>
+      </c>
+      <c r="E131" s="2">
+        <f>(61*(10^2))/0.01</f>
+        <v>610000</v>
+      </c>
+      <c r="F131" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>10</v>
+      </c>
+      <c r="B132" t="s">
+        <v>21</v>
+      </c>
+      <c r="C132" t="s">
+        <v>5</v>
+      </c>
+      <c r="D132" s="2">
+        <f>(26*(10^4))/0.01</f>
+        <v>26000000</v>
+      </c>
+      <c r="E132" s="2">
+        <f>(20*(10^4))/0.01</f>
+        <v>20000000</v>
+      </c>
+      <c r="F132" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>11</v>
+      </c>
+      <c r="B133" t="s">
+        <v>21</v>
+      </c>
+      <c r="C133" t="s">
+        <v>5</v>
+      </c>
+      <c r="D133" s="2">
+        <f>(19*(10^3))/0.01</f>
+        <v>1900000</v>
+      </c>
+      <c r="E133" s="2">
+        <f>(38*(10^2))/0.01</f>
+        <v>380000</v>
+      </c>
+      <c r="F133" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>12</v>
+      </c>
+      <c r="B134" t="s">
+        <v>21</v>
+      </c>
+      <c r="C134" t="s">
+        <v>5</v>
+      </c>
+      <c r="D134" s="2">
+        <f>(3*(10^0))/0.01</f>
+        <v>300</v>
+      </c>
+      <c r="E134" s="2">
+        <f>(12*(10^0))/0.01</f>
+        <v>1200</v>
+      </c>
+      <c r="F134" s="2">
+        <f>(1*(10^0))/0.01</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>3</v>
+      </c>
+      <c r="B135" t="s">
+        <v>21</v>
+      </c>
+      <c r="C135" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" s="2">
+        <f>(19*(10^4))/0.01</f>
+        <v>19000000</v>
+      </c>
+      <c r="E135" s="2">
+        <v>0</v>
+      </c>
+      <c r="F135" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>7</v>
+      </c>
+      <c r="B136" t="s">
+        <v>21</v>
+      </c>
+      <c r="C136" t="s">
+        <v>6</v>
+      </c>
+      <c r="D136" s="2">
+        <v>0</v>
+      </c>
+      <c r="E136" s="2">
+        <v>0</v>
+      </c>
+      <c r="F136" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>8</v>
+      </c>
+      <c r="B137" t="s">
+        <v>21</v>
+      </c>
+      <c r="C137" t="s">
+        <v>6</v>
+      </c>
+      <c r="D137" s="2">
+        <v>0</v>
+      </c>
+      <c r="E137" s="2">
+        <v>0</v>
+      </c>
+      <c r="F137" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" t="s">
+        <v>21</v>
+      </c>
+      <c r="C138" t="s">
+        <v>6</v>
+      </c>
+      <c r="D138" s="2">
+        <f>(11*(10^1))/0.01</f>
+        <v>11000</v>
+      </c>
+      <c r="E138" s="2">
+        <f>(28*(10^2))/0.01</f>
+        <v>280000</v>
+      </c>
+      <c r="F138" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>10</v>
+      </c>
+      <c r="B139" t="s">
+        <v>21</v>
+      </c>
+      <c r="C139" t="s">
+        <v>6</v>
+      </c>
+      <c r="D139" s="2">
+        <f>(6*(10^1))/0.01</f>
+        <v>6000</v>
+      </c>
+      <c r="E139" s="2">
+        <f>(5*(10^1))/0.01</f>
+        <v>5000</v>
+      </c>
+      <c r="F139" s="2">
+        <f>(15*(10^1))/0.01</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>11</v>
+      </c>
+      <c r="B140" t="s">
+        <v>21</v>
+      </c>
+      <c r="C140" t="s">
+        <v>6</v>
+      </c>
+      <c r="D140" s="2">
+        <f>(50*(10^1))/0.01</f>
+        <v>50000</v>
+      </c>
+      <c r="E140" s="2">
+        <f>(25*(10^1))/0.01</f>
+        <v>25000</v>
+      </c>
+      <c r="F140" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>12</v>
+      </c>
+      <c r="B141" t="s">
+        <v>21</v>
+      </c>
+      <c r="C141" t="s">
+        <v>6</v>
+      </c>
+      <c r="D141" s="2">
+        <v>0</v>
+      </c>
+      <c r="E141" s="2">
+        <f>(6*(10^0))/0.01</f>
+        <v>600</v>
+      </c>
+      <c r="F141" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>3</v>
+      </c>
+      <c r="B142" t="s">
+        <v>22</v>
+      </c>
+      <c r="C142" t="s">
+        <v>5</v>
+      </c>
+      <c r="D142" s="2">
+        <f>(20*(10^4))/0.01</f>
+        <v>20000000</v>
+      </c>
+      <c r="E142" s="2">
+        <f>(23*(10^2))/0.01</f>
+        <v>230000</v>
+      </c>
+      <c r="F142" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>7</v>
+      </c>
+      <c r="B143" t="s">
+        <v>22</v>
+      </c>
+      <c r="C143" t="s">
+        <v>5</v>
+      </c>
+      <c r="D143" s="2">
+        <v>0</v>
+      </c>
+      <c r="E143" s="2">
+        <f>(23*(10^5))/0.01</f>
+        <v>230000000</v>
+      </c>
+      <c r="F143" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>8</v>
+      </c>
+      <c r="B144" t="s">
+        <v>22</v>
+      </c>
+      <c r="C144" t="s">
+        <v>5</v>
+      </c>
+      <c r="D144" s="2">
+        <f>(4*(10^3))/0.01</f>
+        <v>400000</v>
+      </c>
+      <c r="E144" s="2">
+        <f>(23*(10^3))/0.01</f>
+        <v>2300000</v>
+      </c>
+      <c r="F144" s="2">
+        <f>(2*(10^3))/0.01</f>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>9</v>
+      </c>
+      <c r="B145" t="s">
+        <v>22</v>
+      </c>
+      <c r="C145" t="s">
+        <v>5</v>
+      </c>
+      <c r="D145" s="2">
+        <f>(27*(10^4))/0.01</f>
+        <v>27000000</v>
+      </c>
+      <c r="E145" s="2">
+        <f>(14*(10^4))/0.01</f>
+        <v>14000000</v>
+      </c>
+      <c r="F145" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>10</v>
+      </c>
+      <c r="B146" t="s">
+        <v>22</v>
+      </c>
+      <c r="C146" t="s">
+        <v>5</v>
+      </c>
+      <c r="D146" s="2">
+        <f>(39*(10^4))/0.01</f>
+        <v>39000000</v>
+      </c>
+      <c r="E146" s="2">
+        <f>(20*(10^4))/0.01</f>
+        <v>20000000</v>
+      </c>
+      <c r="F146" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>11</v>
+      </c>
+      <c r="B147" t="s">
+        <v>22</v>
+      </c>
+      <c r="C147" t="s">
+        <v>5</v>
+      </c>
+      <c r="D147" s="2">
+        <f>(13*(10^4))/0.01</f>
+        <v>13000000</v>
+      </c>
+      <c r="E147" s="2">
+        <f>(6*(10^4))/0.01</f>
+        <v>6000000</v>
+      </c>
+      <c r="F147" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>12</v>
+      </c>
+      <c r="B148" t="s">
+        <v>22</v>
+      </c>
+      <c r="C148" t="s">
+        <v>5</v>
+      </c>
+      <c r="D148" s="2">
+        <f>(2*(10^1))/0.01</f>
+        <v>2000</v>
+      </c>
+      <c r="E148" s="2">
+        <f>(19*(10^1))/0.01</f>
+        <v>19000</v>
+      </c>
+      <c r="F148" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>3</v>
+      </c>
+      <c r="B149" t="s">
+        <v>22</v>
+      </c>
+      <c r="C149" t="s">
+        <v>6</v>
+      </c>
+      <c r="D149" s="2">
+        <f>(89*(10^3))/0.01</f>
+        <v>8900000</v>
+      </c>
+      <c r="E149" s="2">
+        <v>0</v>
+      </c>
+      <c r="F149" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>7</v>
+      </c>
+      <c r="B150" t="s">
+        <v>22</v>
+      </c>
+      <c r="C150" t="s">
+        <v>6</v>
+      </c>
+      <c r="D150" s="2">
+        <v>0</v>
+      </c>
+      <c r="E150" s="2">
+        <v>0</v>
+      </c>
+      <c r="F150" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>8</v>
+      </c>
+      <c r="B151" t="s">
+        <v>22</v>
+      </c>
+      <c r="C151" t="s">
+        <v>6</v>
+      </c>
+      <c r="D151" s="2">
+        <v>0</v>
+      </c>
+      <c r="E151" s="2">
+        <v>0</v>
+      </c>
+      <c r="F151" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>9</v>
+      </c>
+      <c r="B152" t="s">
+        <v>22</v>
+      </c>
+      <c r="C152" t="s">
+        <v>6</v>
+      </c>
+      <c r="D152" s="2">
+        <f>(20*(10^2))/0.01</f>
+        <v>200000</v>
+      </c>
+      <c r="E152" s="2">
+        <f>(72*(10^3))/0.01</f>
+        <v>7200000</v>
+      </c>
+      <c r="F152" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>10</v>
+      </c>
+      <c r="B153" t="s">
+        <v>22</v>
+      </c>
+      <c r="C153" t="s">
+        <v>6</v>
+      </c>
+      <c r="D153" s="2">
+        <f>(32*(10^0))/0.01</f>
+        <v>3200</v>
+      </c>
+      <c r="E153" s="2">
+        <f>(19*(10^0))/0.01</f>
+        <v>1900</v>
+      </c>
+      <c r="F153" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>11</v>
+      </c>
+      <c r="B154" t="s">
+        <v>22</v>
+      </c>
+      <c r="C154" t="s">
+        <v>6</v>
+      </c>
+      <c r="D154" s="2">
+        <f>(6*(10^2))/0.01</f>
+        <v>60000</v>
+      </c>
+      <c r="E154" s="2">
+        <f>(24*(10^3))/0.01</f>
+        <v>2400000</v>
+      </c>
+      <c r="F154" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>12</v>
+      </c>
+      <c r="B155" t="s">
+        <v>22</v>
+      </c>
+      <c r="C155" t="s">
+        <v>6</v>
+      </c>
+      <c r="D155" s="2">
+        <v>0</v>
+      </c>
+      <c r="E155" s="2">
+        <f>(15*(10^1))/0.01</f>
+        <v>15000</v>
+      </c>
+      <c r="F155" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>3</v>
+      </c>
+      <c r="B156" t="s">
+        <v>23</v>
+      </c>
+      <c r="C156" t="s">
+        <v>5</v>
+      </c>
+      <c r="D156" s="2">
+        <f>(43*(10^3))/0.01</f>
+        <v>4300000</v>
+      </c>
+      <c r="E156" s="2">
+        <f>(16*(10^2))/0.01</f>
+        <v>160000</v>
+      </c>
+      <c r="F156" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>7</v>
+      </c>
+      <c r="B157" t="s">
+        <v>23</v>
+      </c>
+      <c r="C157" t="s">
+        <v>5</v>
+      </c>
+      <c r="D157" s="2">
+        <f>(3*(10^3))/0.01</f>
+        <v>300000</v>
+      </c>
+      <c r="E157" s="2">
+        <f>(55*(10^4))/0.01</f>
+        <v>55000000</v>
+      </c>
+      <c r="F157" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>8</v>
+      </c>
+      <c r="B158" t="s">
+        <v>23</v>
+      </c>
+      <c r="C158" t="s">
+        <v>5</v>
+      </c>
+      <c r="D158" s="2">
+        <f>(10*(10^2))/0.01</f>
+        <v>100000</v>
+      </c>
+      <c r="E158" s="2">
+        <f>(74*(10^2))/0.01</f>
+        <v>740000</v>
+      </c>
+      <c r="F158" s="2">
+        <f>(3*(10^2))/0.01</f>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>9</v>
+      </c>
+      <c r="B159" t="s">
+        <v>23</v>
+      </c>
+      <c r="C159" t="s">
+        <v>5</v>
+      </c>
+      <c r="D159" s="2">
+        <f>(8*(10^3))/0.01</f>
+        <v>800000</v>
+      </c>
+      <c r="E159" s="2">
+        <f>(36*(10^3))/0.01</f>
+        <v>3600000</v>
+      </c>
+      <c r="F159" s="2">
+        <f>(1*(10^2))/0.01</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>10</v>
+      </c>
+      <c r="B160" t="s">
+        <v>23</v>
+      </c>
+      <c r="C160" t="s">
+        <v>5</v>
+      </c>
+      <c r="D160" s="2">
+        <f>(24*(10^3))/0.01</f>
+        <v>2400000</v>
+      </c>
+      <c r="E160" s="2">
+        <f>(32*(10^3))/0.01</f>
+        <v>3200000</v>
+      </c>
+      <c r="F160" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>11</v>
+      </c>
+      <c r="B161" t="s">
+        <v>23</v>
+      </c>
+      <c r="C161" t="s">
+        <v>5</v>
+      </c>
+      <c r="D161" s="2">
+        <f>(16*(10^4))/0.01</f>
+        <v>16000000</v>
+      </c>
+      <c r="E161" s="2">
+        <f>(4*(10^3))/0.01</f>
+        <v>400000</v>
+      </c>
+      <c r="F161" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>12</v>
+      </c>
+      <c r="B162" t="s">
+        <v>23</v>
+      </c>
+      <c r="C162" t="s">
+        <v>5</v>
+      </c>
+      <c r="D162" s="2">
+        <f>(1*(10^0))/0.01</f>
+        <v>100</v>
+      </c>
+      <c r="E162" s="2">
+        <f>(21*(10^2))/0.01</f>
+        <v>210000</v>
+      </c>
+      <c r="F162" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>3</v>
+      </c>
+      <c r="B163" t="s">
+        <v>23</v>
+      </c>
+      <c r="C163" t="s">
+        <v>6</v>
+      </c>
+      <c r="D163" s="2">
+        <f>(32*(10^3))/0.01</f>
+        <v>3200000</v>
+      </c>
+      <c r="E163" s="2">
+        <f>(10*(10^1))/0.01</f>
+        <v>10000</v>
+      </c>
+      <c r="F163" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>7</v>
+      </c>
+      <c r="B164" t="s">
+        <v>23</v>
+      </c>
+      <c r="C164" t="s">
+        <v>6</v>
+      </c>
+      <c r="D164" s="2">
+        <v>0</v>
+      </c>
+      <c r="E164" s="2">
+        <v>0</v>
+      </c>
+      <c r="F164" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>8</v>
+      </c>
+      <c r="B165" t="s">
+        <v>23</v>
+      </c>
+      <c r="C165" t="s">
+        <v>6</v>
+      </c>
+      <c r="D165" s="2">
+        <v>0</v>
+      </c>
+      <c r="E165" s="2">
+        <v>0</v>
+      </c>
+      <c r="F165" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D166" s="2">
+        <v>0</v>
+      </c>
+      <c r="E166" s="2">
+        <f>(33*(10^3))/0.01</f>
+        <v>3300000</v>
+      </c>
+      <c r="F166" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>10</v>
+      </c>
+      <c r="B167" t="s">
+        <v>23</v>
+      </c>
+      <c r="C167" t="s">
+        <v>6</v>
+      </c>
+      <c r="D167" s="2">
+        <v>0</v>
+      </c>
+      <c r="E167" s="2">
+        <f>(1*(10^0))/0.01</f>
+        <v>100</v>
+      </c>
+      <c r="F167" s="2">
+        <f>(23*(10^0))/0.01</f>
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>11</v>
+      </c>
+      <c r="B168" t="s">
+        <v>23</v>
+      </c>
+      <c r="C168" t="s">
+        <v>6</v>
+      </c>
+      <c r="D168" s="2">
+        <f>(2*(10^0))/0.01</f>
+        <v>200</v>
+      </c>
+      <c r="E168" s="2">
+        <f>(35*(10^1))/0.01</f>
+        <v>35000</v>
+      </c>
+      <c r="F168" s="2">
+        <f>(2*(10^1))/0.01</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>12</v>
+      </c>
+      <c r="B169" t="s">
+        <v>23</v>
+      </c>
+      <c r="C169" t="s">
+        <v>6</v>
+      </c>
+      <c r="D169" s="2">
+        <v>0</v>
+      </c>
+      <c r="E169" s="2">
+        <f>(13*(10^2))/0.01</f>
+        <v>130000</v>
+      </c>
+      <c r="F169" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>3</v>
+      </c>
+      <c r="B170" t="s">
+        <v>24</v>
+      </c>
+      <c r="C170" t="s">
+        <v>5</v>
+      </c>
+      <c r="D170" s="2">
+        <f>(33*(10^3))/0.01</f>
+        <v>3300000</v>
+      </c>
+      <c r="E170" s="2">
+        <f>(19*(10^2))/0.01</f>
+        <v>190000</v>
+      </c>
+      <c r="F170" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>7</v>
+      </c>
+      <c r="B171" t="s">
+        <v>24</v>
+      </c>
+      <c r="C171" t="s">
+        <v>5</v>
+      </c>
+      <c r="D171" s="2">
+        <f>(4*(10^3))/0.01</f>
+        <v>400000</v>
+      </c>
+      <c r="E171" s="2">
+        <f>(35*(10^4))/0.01</f>
+        <v>35000000</v>
+      </c>
+      <c r="F171" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>8</v>
+      </c>
+      <c r="B172" t="s">
+        <v>24</v>
+      </c>
+      <c r="C172" t="s">
+        <v>5</v>
+      </c>
+      <c r="D172" s="2">
+        <f>(2*(10^3))/0.01</f>
+        <v>200000</v>
+      </c>
+      <c r="E172" s="2">
+        <f>(18*(10^3))/0.01</f>
+        <v>1800000</v>
+      </c>
+      <c r="F172" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>9</v>
+      </c>
+      <c r="B173" t="s">
+        <v>24</v>
+      </c>
+      <c r="C173" t="s">
+        <v>5</v>
+      </c>
+      <c r="D173" s="2">
+        <f>(69*(10^3))/0.01</f>
+        <v>6900000</v>
+      </c>
+      <c r="E173" s="2">
+        <f>(20*(10^4))/0.01</f>
+        <v>20000000</v>
+      </c>
+      <c r="F173" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>10</v>
+      </c>
+      <c r="B174" t="s">
+        <v>24</v>
+      </c>
+      <c r="C174" t="s">
+        <v>5</v>
+      </c>
+      <c r="D174" s="2">
+        <f>(27*(10^3))/0.01</f>
+        <v>2700000</v>
+      </c>
+      <c r="E174" s="2">
+        <f>(66*(10^3))/0.01</f>
+        <v>6600000</v>
+      </c>
+      <c r="F174" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>11</v>
+      </c>
+      <c r="B175" t="s">
+        <v>24</v>
+      </c>
+      <c r="C175" t="s">
+        <v>5</v>
+      </c>
+      <c r="D175" s="2">
+        <f>(28*(10^4))/0.01</f>
+        <v>28000000</v>
+      </c>
+      <c r="E175" s="2">
+        <f>(30*(10^3))/0.01</f>
+        <v>3000000</v>
+      </c>
+      <c r="F175" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>12</v>
+      </c>
+      <c r="B176" t="s">
+        <v>24</v>
+      </c>
+      <c r="C176" t="s">
+        <v>5</v>
+      </c>
+      <c r="D176" s="2">
+        <v>0</v>
+      </c>
+      <c r="E176" s="2">
+        <f>(15*(10^2))/0.01</f>
+        <v>150000</v>
+      </c>
+      <c r="F176" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>3</v>
+      </c>
+      <c r="B177" t="s">
+        <v>24</v>
+      </c>
+      <c r="C177" t="s">
+        <v>6</v>
+      </c>
+      <c r="D177" s="2">
+        <f>(19*(10^3))/0.01</f>
+        <v>1900000</v>
+      </c>
+      <c r="E177" s="2">
+        <f>(11*(10^2))/0.01</f>
+        <v>110000</v>
+      </c>
+      <c r="F177" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>7</v>
+      </c>
+      <c r="B178" t="s">
+        <v>24</v>
+      </c>
+      <c r="C178" t="s">
+        <v>6</v>
+      </c>
+      <c r="D178" s="2">
+        <v>0</v>
+      </c>
+      <c r="E178" s="2">
+        <v>0</v>
+      </c>
+      <c r="F178" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>8</v>
+      </c>
+      <c r="B179" t="s">
+        <v>24</v>
+      </c>
+      <c r="C179" t="s">
+        <v>6</v>
+      </c>
+      <c r="D179" s="2">
+        <v>0</v>
+      </c>
+      <c r="E179" s="2">
+        <v>0</v>
+      </c>
+      <c r="F179" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B180" t="s">
+        <v>24</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D180" s="2">
+        <v>0</v>
+      </c>
+      <c r="E180" s="2">
+        <f>(22*(10^4))/0.01</f>
+        <v>22000000</v>
+      </c>
+      <c r="F180" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>10</v>
+      </c>
+      <c r="B181" t="s">
+        <v>24</v>
+      </c>
+      <c r="C181" t="s">
+        <v>6</v>
+      </c>
+      <c r="D181" s="2">
+        <v>0</v>
+      </c>
+      <c r="E181" s="2">
+        <f>(1*(10^0))/0.01</f>
+        <v>100</v>
+      </c>
+      <c r="F181" s="2">
+        <f>(22*(10^0))/0.01</f>
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>11</v>
+      </c>
+      <c r="B182" t="s">
+        <v>24</v>
+      </c>
+      <c r="C182" t="s">
+        <v>6</v>
+      </c>
+      <c r="D182" s="2">
+        <v>0</v>
+      </c>
+      <c r="E182" s="2">
+        <f>(26*(10^3))/0.01</f>
+        <v>2600000</v>
+      </c>
+      <c r="F182" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>12</v>
+      </c>
+      <c r="B183" t="s">
+        <v>24</v>
+      </c>
+      <c r="C183" t="s">
+        <v>6</v>
+      </c>
+      <c r="D183" s="2">
+        <v>0</v>
+      </c>
+      <c r="E183" s="2">
+        <f>(74*(10^1))/0.01</f>
+        <v>74000</v>
+      </c>
+      <c r="F183" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>3</v>
+      </c>
+      <c r="B184" t="s">
+        <v>25</v>
+      </c>
+      <c r="C184" t="s">
+        <v>5</v>
+      </c>
+      <c r="D184" s="2">
+        <f>(47*(10^3))/0.01</f>
+        <v>4700000</v>
+      </c>
+      <c r="E184" s="2">
+        <f>(57*(10^3))/0.01</f>
+        <v>5700000</v>
+      </c>
+      <c r="F184" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>7</v>
+      </c>
+      <c r="B185" t="s">
+        <v>25</v>
+      </c>
+      <c r="C185" t="s">
+        <v>5</v>
+      </c>
+      <c r="D185" s="2">
+        <f>(27*(10^2))/0.01</f>
+        <v>270000</v>
+      </c>
+      <c r="E185" s="2">
+        <f>(127*(10^3))/0.01</f>
+        <v>12700000</v>
+      </c>
+      <c r="F185" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>8</v>
+      </c>
+      <c r="B186" t="s">
+        <v>25</v>
+      </c>
+      <c r="C186" t="s">
+        <v>5</v>
+      </c>
+      <c r="D186" s="2">
+        <f>(60*(10^3))/0.01</f>
+        <v>6000000</v>
+      </c>
+      <c r="E186" s="2">
+        <f>(52*(10^3))/0.01</f>
+        <v>5200000</v>
+      </c>
+      <c r="F186" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>9</v>
+      </c>
+      <c r="B187" t="s">
+        <v>25</v>
+      </c>
+      <c r="C187" t="s">
+        <v>5</v>
+      </c>
+      <c r="D187" s="2">
+        <f>(14*(10^4))/0.01</f>
+        <v>14000000</v>
+      </c>
+      <c r="E187" s="2">
+        <f>(15*(10^4))/0.01</f>
+        <v>15000000</v>
+      </c>
+      <c r="F187" s="2">
+        <f>(1*(10^4))/0.01</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>10</v>
+      </c>
+      <c r="B188" t="s">
+        <v>25</v>
+      </c>
+      <c r="C188" t="s">
+        <v>5</v>
+      </c>
+      <c r="D188" s="2">
+        <f>(4*(10^4))/0.01</f>
+        <v>4000000</v>
+      </c>
+      <c r="E188" s="2">
+        <f>(12*(10^4))/0.01</f>
+        <v>12000000</v>
+      </c>
+      <c r="F188" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>11</v>
+      </c>
+      <c r="B189" t="s">
+        <v>25</v>
+      </c>
+      <c r="C189" t="s">
+        <v>5</v>
+      </c>
+      <c r="D189" s="2">
+        <f>(12*(10^5))/0.01</f>
+        <v>120000000</v>
+      </c>
+      <c r="E189" s="2">
+        <f>(13*(10^5))/0.01</f>
+        <v>130000000</v>
+      </c>
+      <c r="F189" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>12</v>
+      </c>
+      <c r="B190" t="s">
+        <v>25</v>
+      </c>
+      <c r="C190" t="s">
+        <v>5</v>
+      </c>
+      <c r="D190" s="2">
+        <v>0</v>
+      </c>
+      <c r="E190" s="2">
+        <f>(65*(10^1))/0.01</f>
+        <v>65000</v>
+      </c>
+      <c r="F190" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>3</v>
+      </c>
+      <c r="B191" t="s">
+        <v>25</v>
+      </c>
+      <c r="C191" t="s">
+        <v>6</v>
+      </c>
+      <c r="D191" s="2">
+        <f>(27*(10^3))/0.01</f>
+        <v>2700000</v>
+      </c>
+      <c r="E191" s="2">
+        <f>(56*(10^3))/0.01</f>
+        <v>5600000</v>
+      </c>
+      <c r="F191" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>7</v>
+      </c>
+      <c r="B192" t="s">
+        <v>25</v>
+      </c>
+      <c r="C192" t="s">
+        <v>6</v>
+      </c>
+      <c r="D192" s="2">
+        <v>0</v>
+      </c>
+      <c r="E192" s="2">
+        <v>0</v>
+      </c>
+      <c r="F192" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>8</v>
+      </c>
+      <c r="B193" t="s">
+        <v>25</v>
+      </c>
+      <c r="C193" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" s="2">
+        <v>0</v>
+      </c>
+      <c r="E193" s="2">
+        <v>0</v>
+      </c>
+      <c r="F193" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B194" t="s">
+        <v>25</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" s="2">
+        <v>0</v>
+      </c>
+      <c r="E194" s="2">
+        <f>(38*(10^4))/0.01</f>
+        <v>38000000</v>
+      </c>
+      <c r="F194" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>10</v>
+      </c>
+      <c r="B195" t="s">
+        <v>25</v>
+      </c>
+      <c r="C195" t="s">
+        <v>6</v>
+      </c>
+      <c r="D195" s="2">
+        <v>0</v>
+      </c>
+      <c r="E195" s="2">
+        <v>0</v>
+      </c>
+      <c r="F195" s="2">
+        <f>(4*(10^1))/0.01</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>11</v>
+      </c>
+      <c r="B196" t="s">
+        <v>25</v>
+      </c>
+      <c r="C196" t="s">
+        <v>6</v>
+      </c>
+      <c r="D196" s="2">
+        <v>0</v>
+      </c>
+      <c r="E196" s="2">
+        <f>(39*(10^4))/0.01</f>
+        <v>39000000</v>
+      </c>
+      <c r="F196" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>12</v>
+      </c>
+      <c r="B197" t="s">
+        <v>25</v>
+      </c>
+      <c r="C197" t="s">
+        <v>6</v>
+      </c>
+      <c r="D197" s="2">
+        <v>0</v>
+      </c>
+      <c r="E197" s="2">
+        <f>(8*(10^2))/0.01</f>
+        <v>80000</v>
+      </c>
+      <c r="F197" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
